--- a/GATEWAY/A1#111#WEBCOMNETXX/WebComNet/GesFisioInCloud/1.0.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111#WEBCOMNETXX/WebComNet/GesFisioInCloud/1.0.0/report-checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GATEWAY\A1#111#WEBCOMNETXX\WebComNet\GesFisioInCloud\1.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8FBC3B6-1074-4A49-BCA9-CA5FCA062707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7B6DD9-D6C0-4470-844E-4148C62047A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1730,24 +1730,6 @@
     <t>subject_application_version:1.0.0</t>
   </si>
   <si>
-    <t>2026-01-16T09:06:53+00:00</t>
-  </si>
-  <si>
-    <t>2026-01-16T10:07:25+00:00</t>
-  </si>
-  <si>
-    <t>848b29c4842ccab6cb3d3c87c44d9e45</t>
-  </si>
-  <si>
-    <t>f4202623c023e62334690954e30dffcd</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.30.4.4.88ac032d92c99bdba3af2000dc4ac3dae366744bc0690c18e51ad08e661cee99.805376065a^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.30.4.4.764b614ecc695b7a2be8e887fb0831512dcb60755ba3d777fb9c6abec5f13b8e.14471b693c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>Webcomnet Snc</t>
   </si>
   <si>
@@ -1791,6 +1773,24 @@
   </si>
   <si>
     <t>L'applicativo gestisce prestazioni in accesso diretto senza ricetta medica, pertanto l'elemento inFulfillmentOf/order/priorityCode non viene generato</t>
+  </si>
+  <si>
+    <t>9eab55c6a2a38600781718b5d6eddb7f</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.30.4.4.91f812865fb70ebb4e2c720c635801cd42e361d936155a77769ee7f3aa465748.d74bb2a30d^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-02-18T11:16:31+00:00</t>
+  </si>
+  <si>
+    <t>2026-02-18T11:09:23+00:00</t>
+  </si>
+  <si>
+    <t>97d229653fd51b7858d1919a54783d5c</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.30.4.4.91f812865fb70ebb4e2c720c635801cd42e361d936155a77769ee7f3aa465748.e9e85e1742^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
 </sst>
 </file>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="B2" s="65"/>
       <c r="C2" s="66" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D2" s="65"/>
       <c r="F2" s="5"/>
@@ -4427,13 +4427,13 @@
         <v>46041</v>
       </c>
       <c r="G15" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="H15" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="I15" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="J15" s="36" t="s">
         <v>64</v>
@@ -4447,7 +4447,7 @@
         <v>64</v>
       </c>
       <c r="O15" s="58" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="P15" s="36" t="s">
         <v>226</v>
@@ -4459,7 +4459,7 @@
         <v>226</v>
       </c>
       <c r="S15" s="36" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="T15" s="36"/>
       <c r="U15" s="37"/>
@@ -4747,13 +4747,13 @@
         <v>46041</v>
       </c>
       <c r="G23" s="59" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="H23" s="60" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="I23" s="59" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="J23" s="36" t="s">
         <v>64</v>
@@ -4767,7 +4767,7 @@
         <v>64</v>
       </c>
       <c r="O23" s="58" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="P23" s="36" t="s">
         <v>226</v>
@@ -4779,7 +4779,7 @@
         <v>226</v>
       </c>
       <c r="S23" s="36" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="T23" s="36"/>
       <c r="U23" s="37"/>
@@ -5089,7 +5089,7 @@
         <v>64</v>
       </c>
       <c r="O31" s="36" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="P31" s="36" t="s">
         <v>226</v>
@@ -5101,7 +5101,7 @@
         <v>226</v>
       </c>
       <c r="S31" s="36" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="T31" s="36"/>
       <c r="U31" s="37"/>
@@ -8824,7 +8824,7 @@
         <v>235</v>
       </c>
       <c r="L130" s="54" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="M130" s="54"/>
       <c r="N130" s="54"/>
@@ -10078,16 +10078,16 @@
         <v>379</v>
       </c>
       <c r="F164" s="52">
-        <v>46038</v>
+        <v>46071</v>
       </c>
       <c r="G164" s="52" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="H164" s="52" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="I164" s="53" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="J164" s="54" t="s">
         <v>64</v>
@@ -10133,16 +10133,16 @@
         <v>380</v>
       </c>
       <c r="F165" s="52">
-        <v>46038</v>
+        <v>46071</v>
       </c>
       <c r="G165" s="52" t="s">
-        <v>443</v>
+        <v>459</v>
       </c>
       <c r="H165" s="52" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="I165" s="53" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="J165" s="54" t="s">
         <v>64</v>
@@ -10831,7 +10831,7 @@
         <v>235</v>
       </c>
       <c r="L183" s="49" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="M183" s="54"/>
       <c r="N183" s="54"/>
@@ -11096,7 +11096,7 @@
         <v>235</v>
       </c>
       <c r="L190" s="54" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="M190" s="54"/>
       <c r="N190" s="54"/>
@@ -17456,21 +17456,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BE9A258ADBC3EC4CBEB1E2AB9909207A" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0284f501378927579289f00316ec8a74">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="295b7897-c886-40bf-9750-5782b814c3e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b47213d65be806e283915cff374a7eef" ns2:_="">
     <xsd:import namespace="295b7897-c886-40bf-9750-5782b814c3e4"/>
@@ -17614,10 +17599,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7568E770-0BC4-46AF-B6C6-958AE21C8F7F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="295b7897-c886-40bf-9750-5782b814c3e4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -17640,19 +17650,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7568E770-0BC4-46AF-B6C6-958AE21C8F7F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="295b7897-c886-40bf-9750-5782b814c3e4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/GATEWAY/A1#111#WEBCOMNETXX/WebComNet/GesFisioInCloud/1.0.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111#WEBCOMNETXX/WebComNet/GesFisioInCloud/1.0.0/report-checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GATEWAY\A1#111#WEBCOMNETXX\WebComNet\GesFisioInCloud\1.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{751D9F0C-87EA-49AA-B4EB-926807C300E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{437A5766-C3B9-4D39-A932-875D07815695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="462">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -1745,9 +1745,6 @@
     <t>Errore nella validazione del referto. Token JWT non valido. Il campo purpose_of_use non è valorizzato</t>
   </si>
   <si>
-    <t>Il software mostra l'errore e interrompe l'invio. L'errore non può verificarsi in produzione perché il JWT è generato automaticamente con tutti i campi obbligatori incluso purpose_of_use</t>
-  </si>
-  <si>
     <t>2026-01-19T11:07:10Z</t>
   </si>
   <si>
@@ -1757,9 +1754,6 @@
     <t>Errore nella validazione del referto. Token JWT non valido. Il campo action_id non è valorizzato</t>
   </si>
   <si>
-    <t>Il software mostra l'errore e interrompe l'invio. L'errore non può verificarsi in produzione perché il JWT è generato automaticamente con tutti i campi obbligatori incluso action_id</t>
-  </si>
-  <si>
     <t>Errore di timeout. Riprova</t>
   </si>
   <si>
@@ -1791,6 +1785,9 @@
   </si>
   <si>
     <t>2.16.840.1.113883.2.9.2.30.4.4.ba7d7ae38af04d13cb527ad2ef459947d843159493155c88018966daa44d12b6.8b5ce69bb9^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>Test eseguito con JWT volutamente malformato per verificare la gestione errori. Il software mostra l'errore e interrompe l'invio. In produzione il JWT è sempre generato correttamente dal software.</t>
   </si>
 </sst>
 </file>
@@ -2483,6 +2480,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2504,12 +2507,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3988,14 +3985,14 @@
       <c r="W1" s="8"/>
     </row>
     <row r="2" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="66" t="s">
+      <c r="B2" s="67"/>
+      <c r="C2" s="68" t="s">
         <v>442</v>
       </c>
-      <c r="D2" s="65"/>
+      <c r="D2" s="67"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -4016,14 +4013,14 @@
       <c r="W2" s="8"/>
     </row>
     <row r="3" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="73" t="s">
+      <c r="B3" s="70"/>
+      <c r="C3" s="75" t="s">
         <v>439</v>
       </c>
-      <c r="D3" s="65"/>
+      <c r="D3" s="67"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
@@ -4044,12 +4041,12 @@
       <c r="W3" s="8"/>
     </row>
     <row r="4" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A4" s="69"/>
-      <c r="B4" s="70"/>
-      <c r="C4" s="73" t="s">
+      <c r="A4" s="71"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="75" t="s">
         <v>440</v>
       </c>
-      <c r="D4" s="65"/>
+      <c r="D4" s="67"/>
       <c r="E4" s="3"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
@@ -4071,12 +4068,12 @@
       <c r="W4" s="8"/>
     </row>
     <row r="5" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A5" s="71"/>
-      <c r="B5" s="72"/>
-      <c r="C5" s="73" t="s">
+      <c r="A5" s="73"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="75" t="s">
         <v>441</v>
       </c>
-      <c r="D5" s="65"/>
+      <c r="D5" s="67"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
@@ -4097,8 +4094,8 @@
       <c r="W5" s="8"/>
     </row>
     <row r="6" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A6" s="62"/>
-      <c r="B6" s="63"/>
+      <c r="A6" s="64"/>
+      <c r="B6" s="65"/>
       <c r="C6" s="9"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -4418,7 +4415,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="19.2" customHeight="1" thickBot="1">
+    <row r="15" spans="1:23" ht="17.399999999999999" customHeight="1" thickBot="1">
       <c r="A15" s="33">
         <v>32</v>
       </c>
@@ -4470,7 +4467,7 @@
         <v>226</v>
       </c>
       <c r="S15" s="36" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="T15" s="36"/>
       <c r="U15" s="37"/>
@@ -4758,10 +4755,10 @@
         <v>46041</v>
       </c>
       <c r="G23" s="59" t="s">
+        <v>447</v>
+      </c>
+      <c r="H23" s="60" t="s">
         <v>448</v>
-      </c>
-      <c r="H23" s="60" t="s">
-        <v>449</v>
       </c>
       <c r="I23" s="59" t="s">
         <v>445</v>
@@ -4778,7 +4775,7 @@
         <v>64</v>
       </c>
       <c r="O23" s="58" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="P23" s="36" t="s">
         <v>226</v>
@@ -4790,7 +4787,7 @@
         <v>226</v>
       </c>
       <c r="S23" s="36" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="T23" s="36"/>
       <c r="U23" s="37"/>
@@ -5100,7 +5097,7 @@
         <v>64</v>
       </c>
       <c r="O31" s="36" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="P31" s="36" t="s">
         <v>226</v>
@@ -5109,10 +5106,10 @@
         <v>226</v>
       </c>
       <c r="R31" s="36" t="s">
-        <v>226</v>
+        <v>64</v>
       </c>
       <c r="S31" s="36" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="T31" s="36"/>
       <c r="U31" s="37"/>
@@ -8835,7 +8832,7 @@
         <v>235</v>
       </c>
       <c r="L130" s="54" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="M130" s="54"/>
       <c r="N130" s="54"/>
@@ -10092,13 +10089,13 @@
         <v>46087</v>
       </c>
       <c r="G164" s="52" t="s">
+        <v>455</v>
+      </c>
+      <c r="H164" s="62" t="s">
+        <v>456</v>
+      </c>
+      <c r="I164" s="53" t="s">
         <v>457</v>
-      </c>
-      <c r="H164" s="74" t="s">
-        <v>458</v>
-      </c>
-      <c r="I164" s="53" t="s">
-        <v>459</v>
       </c>
       <c r="J164" s="54" t="s">
         <v>64</v>
@@ -10146,14 +10143,14 @@
       <c r="F165" s="52">
         <v>46087</v>
       </c>
-      <c r="G165" s="75" t="s">
+      <c r="G165" s="63" t="s">
+        <v>458</v>
+      </c>
+      <c r="H165" s="52" t="s">
+        <v>459</v>
+      </c>
+      <c r="I165" s="53" t="s">
         <v>460</v>
-      </c>
-      <c r="H165" s="52" t="s">
-        <v>461</v>
-      </c>
-      <c r="I165" s="53" t="s">
-        <v>462</v>
       </c>
       <c r="J165" s="54" t="s">
         <v>64</v>
@@ -10842,7 +10839,7 @@
         <v>235</v>
       </c>
       <c r="L183" s="49" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="M183" s="54"/>
       <c r="N183" s="54"/>
@@ -11107,7 +11104,7 @@
         <v>235</v>
       </c>
       <c r="L190" s="54" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="M190" s="54"/>
       <c r="N190" s="54"/>
@@ -17467,21 +17464,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BE9A258ADBC3EC4CBEB1E2AB9909207A" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0284f501378927579289f00316ec8a74">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="295b7897-c886-40bf-9750-5782b814c3e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b47213d65be806e283915cff374a7eef" ns2:_="">
     <xsd:import namespace="295b7897-c886-40bf-9750-5782b814c3e4"/>
@@ -17625,10 +17607,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7568E770-0BC4-46AF-B6C6-958AE21C8F7F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="295b7897-c886-40bf-9750-5782b814c3e4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -17651,19 +17658,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7568E770-0BC4-46AF-B6C6-958AE21C8F7F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="295b7897-c886-40bf-9750-5782b814c3e4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/GATEWAY/A1#111#WEBCOMNETXX/WebComNet/GesFisioInCloud/1.0.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111#WEBCOMNETXX/WebComNet/GesFisioInCloud/1.0.0/report-checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GATEWAY\A1#111#WEBCOMNETXX\WebComNet\GesFisioInCloud\1.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{437A5766-C3B9-4D39-A932-875D07815695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E0043B-DF56-4CC6-B522-7DD658C7E7B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1787,7 +1787,7 @@
     <t>2.16.840.1.113883.2.9.2.30.4.4.ba7d7ae38af04d13cb527ad2ef459947d843159493155c88018966daa44d12b6.8b5ce69bb9^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
-    <t>Test eseguito con JWT volutamente malformato per verificare la gestione errori. Il software mostra l'errore e interrompe l'invio. In produzione il JWT è sempre generato correttamente dal software.</t>
+    <t>Il software mostra l'errore all'utente e interrompe l'invio. La risoluzione richiede intervento tecnico. Dopo la correzione, l'operatore potrà procedere con un nuovo invio del documento.</t>
   </si>
 </sst>
 </file>
@@ -4458,7 +4458,7 @@
         <v>446</v>
       </c>
       <c r="P15" s="36" t="s">
-        <v>226</v>
+        <v>64</v>
       </c>
       <c r="Q15" s="36" t="s">
         <v>226</v>
@@ -4778,7 +4778,7 @@
         <v>449</v>
       </c>
       <c r="P23" s="36" t="s">
-        <v>226</v>
+        <v>64</v>
       </c>
       <c r="Q23" s="36" t="s">
         <v>226</v>
@@ -17464,6 +17464,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BE9A258ADBC3EC4CBEB1E2AB9909207A" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0284f501378927579289f00316ec8a74">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="295b7897-c886-40bf-9750-5782b814c3e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b47213d65be806e283915cff374a7eef" ns2:_="">
     <xsd:import namespace="295b7897-c886-40bf-9750-5782b814c3e4"/>
@@ -17607,35 +17622,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7568E770-0BC4-46AF-B6C6-958AE21C8F7F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="295b7897-c886-40bf-9750-5782b814c3e4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -17658,9 +17648,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7568E770-0BC4-46AF-B6C6-958AE21C8F7F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="295b7897-c886-40bf-9750-5782b814c3e4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/GATEWAY/A1#111#WEBCOMNETXX/WebComNet/GesFisioInCloud/1.0.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111#WEBCOMNETXX/WebComNet/GesFisioInCloud/1.0.0/report-checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GATEWAY\A1#111#WEBCOMNETXX\WebComNet\GesFisioInCloud\1.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E0043B-DF56-4CC6-B522-7DD658C7E7B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9D6748-7587-4FCA-9E05-A1A12CE15CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4464,7 +4464,7 @@
         <v>226</v>
       </c>
       <c r="R15" s="36" t="s">
-        <v>226</v>
+        <v>64</v>
       </c>
       <c r="S15" s="36" t="s">
         <v>461</v>
@@ -4784,7 +4784,7 @@
         <v>226</v>
       </c>
       <c r="R23" s="36" t="s">
-        <v>226</v>
+        <v>64</v>
       </c>
       <c r="S23" s="36" t="s">
         <v>461</v>
@@ -17464,18 +17464,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17623,14 +17623,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
@@ -17643,6 +17635,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
